--- a/dataset/Data Halte SuroboyoBus & WaraWiri API.xlsx
+++ b/dataset/Data Halte SuroboyoBus & WaraWiri API.xlsx
@@ -13,31 +13,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="974">
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Nama Halte</t>
-  </si>
-  <si>
-    <t>Rute yang Melewati</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Nama_Halte</t>
+  </si>
+  <si>
+    <t>Rute_yang_Melewati</t>
   </si>
   <si>
     <t>Aditya Warman</t>
   </si>
   <si>
-    <t>K-10 R2</t>
+    <t>tmk2 R2</t>
   </si>
   <si>
     <t>Airlangga Convention Center</t>
   </si>
   <si>
-    <t>K-51 R4</t>
+    <t>sbr4 R4</t>
   </si>
   <si>
     <t>Alas Malang A</t>
   </si>
   <si>
-    <t>K-105 5</t>
+    <t>fd05 5</t>
   </si>
   <si>
     <t>Alas Malang B</t>
@@ -46,13 +46,13 @@
     <t>Alun-Alun Contong</t>
   </si>
   <si>
-    <t>K-1 R1 / K-107 7</t>
+    <t>sbr1 R1 / fd07 7</t>
   </si>
   <si>
     <t>Amir Hamzah A</t>
   </si>
   <si>
-    <t>K-102 2</t>
+    <t>fd02 2</t>
   </si>
   <si>
     <t>Amir Hamzah B</t>
@@ -64,13 +64,13 @@
     <t>Apartemen Dian Sukolilo Regency</t>
   </si>
   <si>
-    <t>K-123 10</t>
+    <t>fd10 10</t>
   </si>
   <si>
     <t>Apartemen Puncak Kertajaya A</t>
   </si>
   <si>
-    <t>K-124 11</t>
+    <t>fd11 11</t>
   </si>
   <si>
     <t>Apartemen Puncak Kertajaya B</t>
@@ -79,7 +79,7 @@
     <t>Babatan A</t>
   </si>
   <si>
-    <t>K-106 6</t>
+    <t>fd06 6</t>
   </si>
   <si>
     <t>Babatan B</t>
@@ -100,13 +100,13 @@
     <t>Balai Kota</t>
   </si>
   <si>
-    <t>K-10 R2 / K-102 2 / K-107 7 / K-121 4</t>
+    <t>tmk2 R2 / fd02 2 / fd07 7 / fd04 4</t>
   </si>
   <si>
     <t>Balai Kota B</t>
   </si>
   <si>
-    <t>K-107 7</t>
+    <t>fd07 7</t>
   </si>
   <si>
     <t>Bambu Runcing</t>
@@ -148,7 +148,7 @@
     <t>Banyu Urip A</t>
   </si>
   <si>
-    <t>K-12 R5</t>
+    <t>sbr5 R5</t>
   </si>
   <si>
     <t>Banyu Urip B</t>
@@ -160,7 +160,7 @@
     <t>Barunawati A</t>
   </si>
   <si>
-    <t>K-1 R1</t>
+    <t>sbr1 R1</t>
   </si>
   <si>
     <t>Barunawati B</t>
@@ -169,7 +169,7 @@
     <t>Basra</t>
   </si>
   <si>
-    <t>K-1 R1 / K-10 R2 / K-12 R5 / K-102 2</t>
+    <t>sbr1 R1 / tmk2 R2 / sbr5 R5 / fd02 2</t>
   </si>
   <si>
     <t>Basra 2</t>
@@ -184,7 +184,7 @@
     <t>Bibis A</t>
   </si>
   <si>
-    <t>K-12 R5 / K-122 9</t>
+    <t>sbr5 R5 / fd09 9</t>
   </si>
   <si>
     <t>Bibis B</t>
@@ -193,7 +193,7 @@
     <t>Biliton 1</t>
   </si>
   <si>
-    <t>K-107 7 / K-121 4</t>
+    <t>fd07 7 / fd04 4</t>
   </si>
   <si>
     <t>Biliton 2</t>
@@ -202,7 +202,7 @@
     <t>Bilka</t>
   </si>
   <si>
-    <t>K-51 R4 / K-108 3</t>
+    <t>sbr4 R4 / fd03 3</t>
   </si>
   <si>
     <t>Bintang Diponggo A</t>
@@ -211,13 +211,13 @@
     <t>Bintang Diponggo B</t>
   </si>
   <si>
-    <t>K-102 2 / K-105 5</t>
+    <t>fd02 2 / fd05 5</t>
   </si>
   <si>
     <t>Bkr Pelajar</t>
   </si>
   <si>
-    <t>K-121 4</t>
+    <t>fd04 4</t>
   </si>
   <si>
     <t>Blauran</t>
@@ -244,7 +244,7 @@
     <t>Bumi Pratama Asri A</t>
   </si>
   <si>
-    <t>K-108 3</t>
+    <t>fd03 3</t>
   </si>
   <si>
     <t>Bumi Pratama Asri B</t>
@@ -259,13 +259,13 @@
     <t>Bundaran ITS</t>
   </si>
   <si>
-    <t>K-10 R2 / K-51 R4 / K-124 11 / K-127 12</t>
+    <t>tmk2 R2 / sbr4 R4 / fd11 11 / fd12 12</t>
   </si>
   <si>
     <t>Bundaran UNESA</t>
   </si>
   <si>
-    <t>K-10 R2 / K-106 6 / K-120 8</t>
+    <t>tmk2 R2 / fd06 6 / fd08 8</t>
   </si>
   <si>
     <t>Bung Tomo</t>
@@ -292,7 +292,7 @@
     <t>Ciliwung A</t>
   </si>
   <si>
-    <t>K-122 9</t>
+    <t>fd09 9</t>
   </si>
   <si>
     <t>Ciliwung B</t>
@@ -307,7 +307,7 @@
     <t>Convention Hall ARH</t>
   </si>
   <si>
-    <t>K-123 10 / K-124 11</t>
+    <t>fd10 10 / fd11 11</t>
   </si>
   <si>
     <t>Darmo</t>
@@ -322,7 +322,7 @@
     <t>Darmo Park 1</t>
   </si>
   <si>
-    <t>K-10 R2 / K-102 2 / K-105 5 / K-122 9</t>
+    <t>tmk2 R2 / fd02 2 / fd05 5 / fd09 9</t>
   </si>
   <si>
     <t>Darmo Park 2</t>
@@ -331,7 +331,7 @@
     <t>Darmo Permai III A</t>
   </si>
   <si>
-    <t>K-105 5 / K-120 8</t>
+    <t>fd05 5 / fd08 8</t>
   </si>
   <si>
     <t>Darmo Permai III B</t>
@@ -373,7 +373,7 @@
     <t>DINAMIKA</t>
   </si>
   <si>
-    <t>K-127 12</t>
+    <t>fd12 12</t>
   </si>
   <si>
     <t>Dinoyo A</t>
@@ -412,7 +412,7 @@
     <t>Dukuh Menanggal</t>
   </si>
   <si>
-    <t>K-1 R1 / K-51 R4 / K-122 9</t>
+    <t>sbr1 R1 / sbr4 R4 / fd09 9</t>
   </si>
   <si>
     <t>Embong Kemiri</t>
@@ -421,7 +421,7 @@
     <t>Embong Malang</t>
   </si>
   <si>
-    <t>K-1 R1 / K-10 R2 / K-12 R5 / K-107 7</t>
+    <t>sbr1 R1 / tmk2 R2 / sbr5 R5 / fd07 7</t>
   </si>
   <si>
     <t>Embong Malang 2</t>
@@ -460,7 +460,7 @@
     <t>GALAXY 1</t>
   </si>
   <si>
-    <t>K-51 R4 / K-127 12</t>
+    <t>sbr4 R4 / fd12 12</t>
   </si>
   <si>
     <t>GALAXY 2</t>
@@ -481,7 +481,7 @@
     <t>Gedung Juang 45</t>
   </si>
   <si>
-    <t>K-10 R2 / K-122 9</t>
+    <t>tmk2 R2 / fd09 9</t>
   </si>
   <si>
     <t>Gedung Pamulangan A</t>
@@ -496,7 +496,7 @@
     <t>Gembong Sawahan A</t>
   </si>
   <si>
-    <t>K-121 4 / K-123 10</t>
+    <t>fd04 4 / fd10 10</t>
   </si>
   <si>
     <t>Gembong Sawahan B</t>
@@ -538,7 +538,7 @@
     <t>Gozco</t>
   </si>
   <si>
-    <t>K-1 R1 / K-10 R2</t>
+    <t>sbr1 R1 / tmk2 R2</t>
   </si>
   <si>
     <t>GPT Kristus Menanggal</t>
@@ -547,7 +547,7 @@
     <t>Graha Family A</t>
   </si>
   <si>
-    <t>K-10 R2 / K-105 5 / K-106 6 / K-120 8</t>
+    <t>tmk2 R2 / fd05 5 / fd06 6 / fd08 8</t>
   </si>
   <si>
     <t>Graha Family B</t>
@@ -565,7 +565,7 @@
     <t>Grand City</t>
   </si>
   <si>
-    <t>K-10 R2 / K-102 2 / K-107 7</t>
+    <t>tmk2 R2 / fd02 2 / fd07 7</t>
   </si>
   <si>
     <t>GRHA Adyatma</t>
@@ -589,7 +589,7 @@
     <t>Gubeng Airlangga</t>
   </si>
   <si>
-    <t>K-10 R2 / K-51 R4</t>
+    <t>tmk2 R2 / sbr4 R4</t>
   </si>
   <si>
     <t>Gubeng Kertajaya A</t>
@@ -631,7 +631,7 @@
     <t>Gunung Anyar Timur A</t>
   </si>
   <si>
-    <t>K-108 3 / K-127 12</t>
+    <t>fd03 3 / fd12 12</t>
   </si>
   <si>
     <t>Gunung Anyar Timur B</t>
@@ -646,7 +646,7 @@
     <t>IKADO A</t>
   </si>
   <si>
-    <t>K-105 5 / K-122 9</t>
+    <t>fd05 5 / fd09 9</t>
   </si>
   <si>
     <t>IKADO B</t>
@@ -679,7 +679,7 @@
     <t>ITATS</t>
   </si>
   <si>
-    <t>K-123 10 / K-124 11 / K-127 12</t>
+    <t>fd10 10 / fd11 11 / fd12 12</t>
   </si>
   <si>
     <t>ITATS 2</t>
@@ -727,7 +727,7 @@
     <t>Jemur Ngawinan</t>
   </si>
   <si>
-    <t>K-1 R1 / K-51 R4</t>
+    <t>sbr1 R1 / sbr4 R4</t>
   </si>
   <si>
     <t>Jemursari A</t>
@@ -760,7 +760,7 @@
     <t>Jono Soewojo 1</t>
   </si>
   <si>
-    <t>K-10 R2 / K-120 8</t>
+    <t>tmk2 R2 / fd08 8</t>
   </si>
   <si>
     <t>Jono Soewojo 2</t>
@@ -769,7 +769,7 @@
     <t>Joyoboyo 2</t>
   </si>
   <si>
-    <t>K-1 R1 / K-106 6 / K-108 3 / K-121 4 / K-122 9</t>
+    <t>sbr1 R1 / fd06 6 / fd03 3 / fd04 4 / fd09 9</t>
   </si>
   <si>
     <t>Kalasan</t>
@@ -784,7 +784,7 @@
     <t>Kaliasin</t>
   </si>
   <si>
-    <t>K-1 R1 / K-10 R2 / K-12 R5</t>
+    <t>sbr1 R1 / tmk2 R2 / sbr5 R5</t>
   </si>
   <si>
     <t>Kalibokor Selatan A</t>
@@ -820,7 +820,7 @@
     <t>Kantor Dinas Kesehatan A</t>
   </si>
   <si>
-    <t>K-51 R4 / K-121 4</t>
+    <t>sbr4 R4 / fd04 4</t>
   </si>
   <si>
     <t>Kantor Dinas Kesehatan B</t>
@@ -910,7 +910,7 @@
     <t>Karangpoh A</t>
   </si>
   <si>
-    <t>K-12 R5 / K-120 8 / K-122 9</t>
+    <t>sbr5 R5 / fd08 8 / fd09 9</t>
   </si>
   <si>
     <t>Karangpoh B</t>
@@ -934,7 +934,7 @@
     <t>KBS</t>
   </si>
   <si>
-    <t>K-106 6 / K-108 3 / K-121 4 / K-122 9</t>
+    <t>fd06 6 / fd03 3 / fd04 4 / fd09 9</t>
   </si>
   <si>
     <t>Kebonsari Tengah A</t>
@@ -1027,7 +1027,7 @@
     <t>KENJERAN PARK</t>
   </si>
   <si>
-    <t>K-124 11 / K-127 12</t>
+    <t>fd11 11 / fd12 12</t>
   </si>
   <si>
     <t>Keputih Makam A</t>
@@ -1054,7 +1054,7 @@
     <t>Kertajaya A</t>
   </si>
   <si>
-    <t>K-10 R2 / K-107 7</t>
+    <t>tmk2 R2 / fd07 7</t>
   </si>
   <si>
     <t>Kertajaya B</t>
@@ -1063,7 +1063,7 @@
     <t>Kertajaya Indah</t>
   </si>
   <si>
-    <t>K-10 R2 / K-51 R4 / K-127 12</t>
+    <t>tmk2 R2 / sbr4 R4 / fd12 12</t>
   </si>
   <si>
     <t>Kertajaya Masjid A</t>
@@ -1081,7 +1081,7 @@
     <t>Ketintang</t>
   </si>
   <si>
-    <t>K-1 R1 / K-121 4 / K-122 9</t>
+    <t>sbr1 R1 / fd04 4 / fd09 9</t>
   </si>
   <si>
     <t>Ketintang Tengah A</t>
@@ -1099,7 +1099,7 @@
     <t>Klampis</t>
   </si>
   <si>
-    <t>K-10 R2 / K-123 10</t>
+    <t>tmk2 R2 / fd10 10</t>
   </si>
   <si>
     <t>Klampis Jaya A</t>
@@ -1222,7 +1222,7 @@
     <t>Manyar</t>
   </si>
   <si>
-    <t>K-51 R4 / K-107 7 / K-108 3 / K-124 11</t>
+    <t>sbr4 R4 / fd07 7 / fd03 3 / fd11 11</t>
   </si>
   <si>
     <t>Manyar 2A</t>
@@ -1282,7 +1282,7 @@
     <t>Margomulyo 1</t>
   </si>
   <si>
-    <t>K-120 8</t>
+    <t>fd08 8</t>
   </si>
   <si>
     <t>Margomulyo 2</t>
@@ -1297,7 +1297,7 @@
     <t>Margorejo</t>
   </si>
   <si>
-    <t>K-1 R1 / K-121 4</t>
+    <t>sbr1 R1 / fd04 4</t>
   </si>
   <si>
     <t>Margorejo 2</t>
@@ -1315,7 +1315,7 @@
     <t>Marvel</t>
   </si>
   <si>
-    <t>K-108 3 / K-121 4</t>
+    <t>fd03 3 / fd04 4</t>
   </si>
   <si>
     <t>Masjid Al Akbar Surabaya</t>
@@ -1339,7 +1339,7 @@
     <t>Maybank Bratang Binangun</t>
   </si>
   <si>
-    <t>K-107 7 / K-108 3</t>
+    <t>fd07 7 / fd03 3</t>
   </si>
   <si>
     <t>Mayjend Sungkono</t>
@@ -1423,7 +1423,7 @@
     <t>Monkasel</t>
   </si>
   <si>
-    <t>K-102 2 / K-107 7</t>
+    <t>fd02 2 / fd07 7</t>
   </si>
   <si>
     <t>Monumen Jenderal Sudirman</t>
@@ -1513,7 +1513,7 @@
     <t>Nginden A</t>
   </si>
   <si>
-    <t>K-51 R4 / K-124 11</t>
+    <t>sbr4 R4 / fd11 11</t>
   </si>
   <si>
     <t>Nginden B</t>
@@ -1570,7 +1570,7 @@
     <t>Pandegiling</t>
   </si>
   <si>
-    <t>K-1 R1 / K-10 R2 / K-102 2</t>
+    <t>sbr1 R1 / tmk2 R2 / fd02 2</t>
   </si>
   <si>
     <t>Pandegiling 2</t>
@@ -1597,7 +1597,7 @@
     <t>Park and Ride Mayjend Sungkono B</t>
   </si>
   <si>
-    <t>K-102 2 / K-105 5 / K-122 9</t>
+    <t>fd02 2 / fd05 5 / fd09 9</t>
   </si>
   <si>
     <t>Pasar Atom 1</t>
@@ -1738,7 +1738,7 @@
     <t>PENS 1 A</t>
   </si>
   <si>
-    <t>K-10 R2 / K-51 R4 / K-124 11</t>
+    <t>tmk2 R2 / sbr4 R4 / fd11 11</t>
   </si>
   <si>
     <t>PENS 2</t>
@@ -2017,7 +2017,7 @@
     <t>RSUD Dr Soetomo 2</t>
   </si>
   <si>
-    <t>K-51 R4 / K-123 10</t>
+    <t>sbr4 R4 / fd10 10</t>
   </si>
   <si>
     <t>RSUD dr. Mohamad Soewandhi</t>
@@ -2071,7 +2071,7 @@
     <t>Samsat Tandes 1</t>
   </si>
   <si>
-    <t>K-12 R5 / K-120 8</t>
+    <t>sbr5 R5 / fd08 8</t>
   </si>
   <si>
     <t>Samsat Tandes 2</t>
@@ -2083,7 +2083,7 @@
     <t>Satelit Indah A</t>
   </si>
   <si>
-    <t>K-120 8 / K-122 9</t>
+    <t>fd08 8 / fd09 9</t>
   </si>
   <si>
     <t>Satelit Indah B</t>
@@ -2344,7 +2344,7 @@
     <t>Sindoro A</t>
   </si>
   <si>
-    <t>K-10 R2 / K-12 R5 / K-107 7</t>
+    <t>tmk2 R2 / sbr5 R5 / fd07 7</t>
   </si>
   <si>
     <t>Singgapur A</t>
@@ -2431,7 +2431,7 @@
     <t>SMPN 3</t>
   </si>
   <si>
-    <t>K-10 R2 / K-12 R5</t>
+    <t>tmk2 R2 / sbr5 R5</t>
   </si>
   <si>
     <t>SMPN 32</t>
@@ -2467,7 +2467,7 @@
     <t>Stasiun Gubeng Baru</t>
   </si>
   <si>
-    <t>K-107 7 / K-123 10</t>
+    <t>fd07 7 / fd10 10</t>
   </si>
   <si>
     <t>Stasiun Pasar Turi</t>
@@ -2698,7 +2698,7 @@
     <t>Terminal Purabaya</t>
   </si>
   <si>
-    <t>K-1 R1 / K-51 R4 / K-127 12</t>
+    <t>sbr1 R1 / sbr4 R4 / fd12 12</t>
   </si>
   <si>
     <t>Terowongan Medokan A</t>
@@ -2737,7 +2737,7 @@
     <t>UBAYA Ngagel A</t>
   </si>
   <si>
-    <t>K-51 R4 / K-107 7 / K-108 3</t>
+    <t>sbr4 R4 / fd07 7 / fd03 3</t>
   </si>
   <si>
     <t>UBAYA Ngagel B</t>
@@ -2827,7 +2827,7 @@
     <t>Urip Sumoharjo 1</t>
   </si>
   <si>
-    <t>K-1 R1 / K-102 2</t>
+    <t>sbr1 R1 / fd02 2</t>
   </si>
   <si>
     <t>Urip Sumoharjo 2</t>
